--- a/public/template-ib-onco.xlsx
+++ b/public/template-ib-onco.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://serviciossaludimssbienestar-my.sharepoint.com/personal/mario_serrano_imssbienestar_gob_mx/Documents/98-IB-onco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{FA0D017F-0EE5-4BAD-BDD4-BCD63342BB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327D0D3C-D592-41FA-94AD-C5BD7E70D626}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{FA0D017F-0EE5-4BAD-BDD4-BCD63342BB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3E05039-A539-48A1-B28D-63FCD75B9E66}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="-3135" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-3255" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="articulos" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">articulos!$C$10:$E$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">articulos!$B$1:$E$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">articulos!$B$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -375,58 +375,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -435,6 +384,27 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -444,19 +414,49 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -760,76 +760,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="e" vm="1">
+      <c r="B1" s="30" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="2:11" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="2:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="32" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="34"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="24"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="13"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="26" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="35"/>
+      <c r="F5" s="34"/>
       <c r="G5" s="2"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="26" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="33">
         <f ca="1">TODAY()</f>
-        <v>46176</v>
-      </c>
-      <c r="F6" s="35"/>
+        <v>46177</v>
+      </c>
+      <c r="F6" s="34"/>
       <c r="G6" s="2"/>
       <c r="H6" s="4"/>
       <c r="I6" s="5"/>
@@ -837,9 +837,9 @@
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="36" t="s">
@@ -848,30 +848,30 @@
       <c r="F7" s="37"/>
       <c r="G7" s="2"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="13"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="27" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="21"/>
       <c r="G8" s="2"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="2:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="14"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -898,6 +898,12 @@
   </sheetData>
   <autoFilter ref="B10:E10" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="13">
+    <mergeCell ref="B4:C9"/>
+    <mergeCell ref="B1:C3"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="D1:F2"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="I7:J7"/>
@@ -905,15 +911,9 @@
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="B4:C9"/>
-    <mergeCell ref="B1:C3"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="D1:F2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294" r:id="rId1"/>
+  <pageSetup scale="90" orientation="portrait" horizontalDpi="4294967294" verticalDpi="4294967294" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/</oddFooter>
   </headerFooter>
